--- a/results/04_final_refined_daily_hydroclimate_data/904/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/904/Daily_all_temperatures.xlsx
@@ -485,15 +485,9 @@
       <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>23</v>
-      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -577,15 +571,9 @@
       <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E6" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>23.7</v>
-      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -600,15 +588,9 @@
       <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E7" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -646,14 +628,10 @@
       <c r="C9" t="n">
         <v>8</v>
       </c>
-      <c r="D9" t="n">
-        <v>26</v>
-      </c>
-      <c r="E9" t="n">
-        <v>17.2</v>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>21.6</v>
+        <v>23.7</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -669,15 +647,9 @@
       <c r="C10" t="n">
         <v>9</v>
       </c>
-      <c r="D10" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E10" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F10" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -692,15 +664,9 @@
       <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="D11" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="E11" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F11" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -732,15 +698,9 @@
       <c r="C13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="E13" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F13" t="n">
-        <v>23.7</v>
-      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -772,15 +732,9 @@
       <c r="C15" t="n">
         <v>14</v>
       </c>
-      <c r="D15" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E15" t="n">
-        <v>18</v>
-      </c>
-      <c r="F15" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -796,13 +750,13 @@
         <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>28.2</v>
+        <v>28.6</v>
       </c>
       <c r="E16" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="F16" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -835,15 +789,9 @@
       <c r="C18" t="n">
         <v>17</v>
       </c>
-      <c r="D18" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="E18" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F18" t="n">
-        <v>23</v>
-      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -875,15 +823,9 @@
       <c r="C20" t="n">
         <v>19</v>
       </c>
-      <c r="D20" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="E20" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="F20" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -898,15 +840,9 @@
       <c r="C21" t="n">
         <v>20</v>
       </c>
-      <c r="D21" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E21" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F21" t="n">
-        <v>22.4</v>
-      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -944,15 +880,9 @@
       <c r="C23" t="n">
         <v>22</v>
       </c>
-      <c r="D23" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E23" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F23" t="n">
-        <v>21.9</v>
-      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -990,15 +920,9 @@
       <c r="C25" t="n">
         <v>24</v>
       </c>
-      <c r="D25" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E25" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F25" t="n">
-        <v>20.9</v>
-      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -1013,15 +937,9 @@
       <c r="C26" t="n">
         <v>25</v>
       </c>
-      <c r="D26" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E26" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F26" t="n">
-        <v>23.2</v>
-      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1060,10 +978,10 @@
         <v>27</v>
       </c>
       <c r="D28" t="n">
-        <v>26.6</v>
+        <v>26.2</v>
       </c>
       <c r="E28" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="F28" t="n">
         <v>22.3</v>
@@ -1082,9 +1000,15 @@
       <c r="C29" t="n">
         <v>28</v>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>21.3</v>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1099,15 +1023,9 @@
       <c r="C30" t="n">
         <v>29</v>
       </c>
-      <c r="D30" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E30" t="n">
-        <v>16</v>
-      </c>
-      <c r="F30" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>

--- a/results/04_final_refined_daily_hydroclimate_data/904/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/904/Daily_all_temperatures.xlsx
@@ -502,15 +502,9 @@
       <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F3" t="n">
-        <v>23</v>
-      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -525,15 +519,9 @@
       <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E4" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F4" t="n">
-        <v>23.2</v>
-      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -548,15 +536,9 @@
       <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E5" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F5" t="n">
-        <v>24.1</v>
-      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -605,15 +587,9 @@
       <c r="C8" t="n">
         <v>7</v>
       </c>
-      <c r="D8" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>18</v>
-      </c>
-      <c r="F8" t="n">
-        <v>23.1</v>
-      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -630,9 +606,7 @@
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>23.7</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -681,9 +655,15 @@
       <c r="C12" t="n">
         <v>11</v>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>22.8</v>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -749,15 +729,9 @@
       <c r="C16" t="n">
         <v>15</v>
       </c>
-      <c r="D16" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E16" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F16" t="n">
-        <v>23</v>
-      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -857,15 +831,9 @@
       <c r="C22" t="n">
         <v>21</v>
       </c>
-      <c r="D22" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E22" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F22" t="n">
-        <v>21.9</v>
-      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -897,15 +865,9 @@
       <c r="C24" t="n">
         <v>23</v>
       </c>
-      <c r="D24" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="E24" t="n">
-        <v>18</v>
-      </c>
-      <c r="F24" t="n">
-        <v>23.1</v>
-      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -954,15 +916,9 @@
       <c r="C27" t="n">
         <v>26</v>
       </c>
-      <c r="D27" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E27" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F27" t="n">
-        <v>22.6</v>
-      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -977,15 +933,9 @@
       <c r="C28" t="n">
         <v>27</v>
       </c>
-      <c r="D28" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E28" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F28" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -1000,15 +950,9 @@
       <c r="C29" t="n">
         <v>28</v>
       </c>
-      <c r="D29" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E29" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F29" t="n">
-        <v>21.3</v>
-      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>

--- a/results/04_final_refined_daily_hydroclimate_data/904/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/904/Daily_all_temperatures.xlsx
@@ -485,9 +485,15 @@
       <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>23</v>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -502,9 +508,15 @@
       <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>23</v>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -536,9 +548,15 @@
       <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>24.1</v>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -570,9 +588,15 @@
       <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>22.6</v>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -587,9 +611,15 @@
       <c r="C8" t="n">
         <v>7</v>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>18</v>
+      </c>
+      <c r="F8" t="n">
+        <v>23.1</v>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -604,9 +634,15 @@
       <c r="C9" t="n">
         <v>8</v>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>26</v>
+      </c>
+      <c r="E9" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>21.6</v>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -621,9 +657,15 @@
       <c r="C10" t="n">
         <v>9</v>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>23.3</v>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -638,9 +680,15 @@
       <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>23.3</v>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -656,13 +704,13 @@
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>27.8</v>
+        <v>30.4</v>
       </c>
       <c r="E12" t="n">
         <v>17.8</v>
       </c>
       <c r="F12" t="n">
-        <v>22.8</v>
+        <v>24.1</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -678,9 +726,15 @@
       <c r="C13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E13" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>23.7</v>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -695,9 +749,15 @@
       <c r="C14" t="n">
         <v>13</v>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>23.8</v>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -712,9 +772,15 @@
       <c r="C15" t="n">
         <v>14</v>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>18</v>
+      </c>
+      <c r="F15" t="n">
+        <v>22.4</v>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -729,9 +795,15 @@
       <c r="C16" t="n">
         <v>15</v>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>23.5</v>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -746,9 +818,15 @@
       <c r="C17" t="n">
         <v>16</v>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>23</v>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -763,9 +841,15 @@
       <c r="C18" t="n">
         <v>17</v>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>22.3</v>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -780,9 +864,15 @@
       <c r="C19" t="n">
         <v>18</v>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>22.3</v>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -797,9 +887,15 @@
       <c r="C20" t="n">
         <v>19</v>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E20" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>19.8</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -814,9 +910,15 @@
       <c r="C21" t="n">
         <v>20</v>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E21" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>22.1</v>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -882,9 +984,15 @@
       <c r="C25" t="n">
         <v>24</v>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E25" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F25" t="n">
+        <v>23.2</v>
+      </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -933,9 +1041,15 @@
       <c r="C28" t="n">
         <v>27</v>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>22.3</v>
+      </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -950,9 +1064,15 @@
       <c r="C29" t="n">
         <v>28</v>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>21.9</v>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -984,9 +1104,15 @@
       <c r="C31" t="n">
         <v>30</v>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>15</v>
+      </c>
+      <c r="F31" t="n">
+        <v>22.8</v>
+      </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>

--- a/results/04_final_refined_daily_hydroclimate_data/904/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/904/Daily_all_temperatures.xlsx
@@ -532,7 +532,9 @@
         <v>3</v>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>17.8</v>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -588,15 +590,9 @@
       <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E7" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F7" t="n">
-        <v>22.6</v>
-      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -681,10 +677,10 @@
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>28.2</v>
+        <v>28.8</v>
       </c>
       <c r="E11" t="n">
-        <v>17.2</v>
+        <v>17.8</v>
       </c>
       <c r="F11" t="n">
         <v>23.3</v>
@@ -703,15 +699,9 @@
       <c r="C12" t="n">
         <v>11</v>
       </c>
-      <c r="D12" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E12" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F12" t="n">
-        <v>24.1</v>
-      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -750,13 +740,13 @@
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>33.3</v>
+        <v>30.6</v>
       </c>
       <c r="E14" t="n">
-        <v>14.3</v>
+        <v>18.2</v>
       </c>
       <c r="F14" t="n">
-        <v>23.8</v>
+        <v>24.4</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -772,15 +762,9 @@
       <c r="C15" t="n">
         <v>14</v>
       </c>
-      <c r="D15" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E15" t="n">
-        <v>18</v>
-      </c>
-      <c r="F15" t="n">
-        <v>22.4</v>
-      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -795,15 +779,9 @@
       <c r="C16" t="n">
         <v>15</v>
       </c>
-      <c r="D16" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="E16" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F16" t="n">
-        <v>23.5</v>
-      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -818,15 +796,9 @@
       <c r="C17" t="n">
         <v>16</v>
       </c>
-      <c r="D17" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="E17" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="F17" t="n">
-        <v>23</v>
-      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -841,15 +813,9 @@
       <c r="C18" t="n">
         <v>17</v>
       </c>
-      <c r="D18" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E18" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F18" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -864,15 +830,9 @@
       <c r="C19" t="n">
         <v>18</v>
       </c>
-      <c r="D19" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E19" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F19" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -887,15 +847,9 @@
       <c r="C20" t="n">
         <v>19</v>
       </c>
-      <c r="D20" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E20" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F20" t="n">
-        <v>19.8</v>
-      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1007,9 +961,13 @@
       <c r="C26" t="n">
         <v>25</v>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>12.8</v>
+      </c>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>7.3</v>
+      </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1024,9 +982,15 @@
       <c r="C27" t="n">
         <v>26</v>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="D27" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F27" t="n">
+        <v>22.6</v>
+      </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -1041,15 +1005,9 @@
       <c r="C28" t="n">
         <v>27</v>
       </c>
-      <c r="D28" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E28" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F28" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -1068,10 +1026,10 @@
         <v>25.4</v>
       </c>
       <c r="E29" t="n">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="F29" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
@@ -1104,15 +1062,9 @@
       <c r="C31" t="n">
         <v>30</v>
       </c>
-      <c r="D31" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E31" t="n">
-        <v>15</v>
-      </c>
-      <c r="F31" t="n">
-        <v>22.8</v>
-      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
